--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92995088673</v>
+        <v>46157.93083994184</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93083994184</v>
+        <v>46157.93353173599</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93353173599</v>
+        <v>46157.93642799684</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93642799684</v>
+        <v>46158.28178517077</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28178517077</v>
+        <v>46158.2975465603</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -721,10 +721,10 @@
         </is>
       </c>
       <c r="D9" s="12" t="n">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46157.92971160259</v>
+        <v>46158.29723347491</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46156.85593831811</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46157.92971160259</v>
+        <v>46158.29723347491</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2975465603</v>
+        <v>46158.29773252769</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29773252769</v>
+        <v>46158.30446742446</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.30446742446</v>
+        <v>46158.33341843446</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33341843446</v>
+        <v>46158.37202323259</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/10_Зарплаты/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.37202323259</v>
+        <v>46158.37419123301</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
@@ -724,7 +724,7 @@
         <v>7.2</v>
       </c>
       <c r="E9" s="13" t="n">
-        <v>46158.29723347491</v>
+        <v>46158.3738060467</v>
       </c>
       <c r="F9" s="9" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>46156.85593831811</v>
       </c>
       <c r="H5" s="17" t="n">
-        <v>46158.29723347491</v>
+        <v>46158.3738060467</v>
       </c>
     </row>
     <row r="6" ht="15" customHeight="1">
